--- a/output/pdf_financials_xlsx/CRDL.xlsx
+++ b/output/pdf_financials_xlsx/CRDL.xlsx
@@ -817,31 +817,31 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.006118</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.103306</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.245422</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.076583</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.106001</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>1.237632</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>2.038465</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>1.193342</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.726401</v>
       </c>
     </row>
     <row r="13">
@@ -1467,16 +1467,16 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-31.638244</v>
+        <v>-31.744245</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-30.930647</v>
+        <v>-32.168279</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-28.128292</v>
+        <v>-30.166757</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-36.677299</v>
+        <v>-37.870641</v>
       </c>
       <c r="J27" s="1" t="inlineStr">
         <is>
@@ -1545,16 +1545,16 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-31.5538</v>
+        <v>-31.659801</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-30.846203</v>
+        <v>-32.083835</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-28.043848</v>
+        <v>-30.082313</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-36.466941</v>
+        <v>-37.660283</v>
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-40063.23006602336</v>
+        <v>-40197.81742001016</v>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -13435,7 +13435,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -14448,7 +14448,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -15493,7 +15493,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E174" s="5" t="n">

--- a/output/pdf_financials_xlsx/CRDL.xlsx
+++ b/output/pdf_financials_xlsx/CRDL.xlsx
@@ -1494,28 +1494,28 @@
         <v>0.050206</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.08444400000000001</v>
+        <v>0.091492</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.08444400000000001</v>
+        <v>0.150572</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.08444400000000001</v>
+        <v>0.229539</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.08444400000000001</v>
+        <v>0.220421</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.08444400000000001</v>
+        <v>0.219908</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.08444400000000001</v>
+        <v>0.248355</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.210358</v>
+        <v>0.373114</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.101983</v>
       </c>
     </row>
     <row r="29">
@@ -1545,16 +1545,16 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-31.659801</v>
+        <v>-31.523824</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-32.083835</v>
+        <v>-31.948371</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-30.082313</v>
+        <v>-29.918402</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-37.660283</v>
+        <v>-37.497527</v>
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-40197.81742001016</v>
+        <v>-40025.17013712545</v>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
@@ -4107,31 +4107,31 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.050206</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.091492</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.150572</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.229539</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.220421</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.219908</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.248355</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.373114</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.101983</v>
       </c>
     </row>
     <row r="101">
@@ -8550,7 +8550,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -8605,7 +8609,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E56" s="5" t="n">
@@ -10082,7 +10086,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -10139,7 +10147,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -13899,7 +13907,11 @@
           <t>Depreciation of property and equipment (note 6)</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -13960,7 +13972,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -15001,7 +15013,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E166" s="5" t="n">

--- a/output/pdf_financials_xlsx/CRDL.xlsx
+++ b/output/pdf_financials_xlsx/CRDL.xlsx
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.021943</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>-0.013791</v>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>0</v>
+        <v>-0.007228</v>
       </c>
       <c r="C116" s="3" t="n">
         <v>0</v>
@@ -5281,7 +5281,7 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.021943</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>-0.013791</v>
@@ -5315,7 +5315,7 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-1.292194</v>
+        <v>-1.314137</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-10.907796</v>
@@ -11736,7 +11736,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E111" s="5" t="n">
         <v>-0.021943</v>
       </c>
@@ -11795,7 +11799,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E112" s="5" t="n">
         <v>-0.007228</v>
       </c>
@@ -12049,7 +12057,11 @@
           <t>Purchase of intangible assets $</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E116" s="5" t="n">
         <v>0.76</v>
       </c>
